--- a/config/auto_configs/2011_Hyundai_Hyundai_Sonata(YFA)_G 2.0 T-GDI.xlsx
+++ b/config/auto_configs/2011_Hyundai_Hyundai_Sonata(YFA)_G 2.0 T-GDI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMA_0025D</t>
+          <t>HMA_001A6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C1638</t>
+          <t>B1395</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ESC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HMA_001A6</t>
+          <t>HMA_00205</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B1395</t>
+          <t>C1275</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C1275</t>
+          <t>C1358</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C1358</t>
+          <t>C1638</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -630,20 +630,592 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HMA_00205</t>
+          <t>HMA_0048F</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C1638</t>
+          <t>P0109</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P0320</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P0340</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P0451</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>P0452</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P0453</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P0454</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P1326</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P1505</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P1506</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P1507</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P1508</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P1691</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P169A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P2135</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P2231</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P2280</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P2A01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>U0155</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HMA_0048F</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>U1111</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HMA_00021</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P0705</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HMA_00021</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>U0001</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HMA_00021</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>U0100</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TPMS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HMA_0002A</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HMA_003A4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IMM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HMA_00029</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ODS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HMA_001A8</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>00</t>
         </is>
